--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2022_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2022_magallanes.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:44</t>
+    <t xml:space="preserve">2026-09-09 20:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_mat_a_2022_magallanes.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_mat_a_2022_magallanes.xlsx
@@ -24,27 +24,27 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Punta Arenas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laguna Blanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Verde</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cabo de Hornos</t>
   </si>
   <si>
-    <t xml:space="preserve">Laguna Blanca</t>
+    <t xml:space="preserve">Porvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primavera</t>
   </si>
   <si>
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">Porvenir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primavera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Punta Arenas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Río Verde</t>
-  </si>
-  <si>
     <t xml:space="preserve">Timaukel</t>
   </si>
   <si>
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:48</t>
+    <t xml:space="preserve">2026-09-18 10:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -469,7 +469,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>78.71</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>74.29</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>77.79</v>
+        <v>78.71</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>80.21</v>
+        <v>77.79</v>
       </c>
     </row>
     <row r="7">
@@ -509,7 +509,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>76.62</v>
+        <v>80.21</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60</v>
+        <v>74.29</v>
       </c>
     </row>
     <row r="9">
